--- a/Thesis/expected_load.xlsx
+++ b/Thesis/expected_load.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://rockmtnins-my.sharepoint.com/personal/abigail_weeks_rmi_org/Documents/Documents/GitHub/Thesis/Thesis/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="129" documentId="8_{6D7D875F-7871-42EB-AB26-F74FA4D8025F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B61873B-CC6B-42C9-9C76-563089393386}"/>
+  <xr:revisionPtr revIDLastSave="130" documentId="8_{6D7D875F-7871-42EB-AB26-F74FA4D8025F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8903F76F-D71D-47C0-AFF0-AC07EF21B1A9}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{92A38E23-1D92-4025-897C-B9789D11F4A6}"/>
+    <workbookView xWindow="2660" yWindow="2660" windowWidth="14400" windowHeight="8170" xr2:uid="{92A38E23-1D92-4025-897C-B9789D11F4A6}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -38,9 +38,6 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
   <si>
-    <t>step</t>
-  </si>
-  <si>
     <t>expected_load</t>
   </si>
   <si>
@@ -48,6 +45,9 @@
   </si>
   <si>
     <t>gw</t>
+  </si>
+  <si>
+    <t>Step</t>
   </si>
 </sst>
 </file>
@@ -496,16 +496,16 @@
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1">
       <c r="A1" t="s">
+        <v>3</v>
+      </c>
+      <c r="B1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="C1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="D1" t="s">
         <v>2</v>
-      </c>
-      <c r="D1" t="s">
-        <v>3</v>
       </c>
     </row>
     <row r="2" spans="1:6" ht="15" thickBot="1">
